--- a/artfynd/A 60665-2021 artfynd.xlsx
+++ b/artfynd/A 60665-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60665-2021 artfynd.xlsx
+++ b/artfynd/A 60665-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>74112494</v>
       </c>
       <c r="B2" t="n">
-        <v>97822</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720618.0233969695</v>
+        <v>720618</v>
       </c>
       <c r="R2" t="n">
-        <v>6394256.158687472</v>
+        <v>6394256</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74112466</v>
+        <v>134303518</v>
       </c>
       <c r="B3" t="n">
-        <v>77998</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1026</v>
+        <v>783</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720627.8232490299</v>
+        <v>720619</v>
       </c>
       <c r="R3" t="n">
-        <v>6394234.162893044</v>
+        <v>6394256</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -855,26 +835,21 @@
           <t>Bäl</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>I-Got-4673</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,50 +858,34 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>74112465</v>
       </c>
       <c r="B4" t="n">
-        <v>77998</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -954,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720629.1471314229</v>
+        <v>720629</v>
       </c>
       <c r="R4" t="n">
-        <v>6394219.751153229</v>
+        <v>6394220</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,19 +946,9 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,6 +972,118 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>74112466</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79837</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Megalaria grossa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bäl-Gane, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>720628</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6394234</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60665-2021 artfynd.xlsx
+++ b/artfynd/A 60665-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134303518</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112465</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,8 +1104,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112466</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>